--- a/docs/pension_data_combined_2026-08-21.xlsx
+++ b/docs/pension_data_combined_2026-08-21.xlsx
@@ -1246,7 +1246,7 @@
         <v>2.1642</v>
       </c>
       <c r="D49" t="n">
-        <v>70440340.81</v>
+        <v>70428314.5</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1817</v>
       </c>
       <c r="D50" t="n">
-        <v>229423669.21</v>
+        <v>229426648.4</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.1989</v>
       </c>
       <c r="D51" t="n">
-        <v>351158187.8</v>
+        <v>351168478</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2051</v>
       </c>
       <c r="D52" t="n">
-        <v>428942715.22</v>
+        <v>428977158.9</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9767</v>
       </c>
       <c r="D53" t="n">
-        <v>396099579.95</v>
+        <v>396140685.3</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.544</v>
       </c>
       <c r="D54" t="n">
-        <v>324369365.39</v>
+        <v>324086548.4</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.202</v>
       </c>
       <c r="D55" t="n">
-        <v>60320284.29</v>
+        <v>60259087.13</v>
       </c>
     </row>
   </sheetData>
